--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1284047-46-CM26</t>
+          <t>1224957-567-CM26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.057.349-8</t>
+          <t>70.932.800-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28640.59</v>
+        <v>17358.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1224957-567-CM26</t>
+          <t>1224957-568-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>17358.05</v>
+        <v>757.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1224957-568-CM26</t>
+          <t>2674-664-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.932.800-K</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE NUNOA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>757.65</v>
+        <v>29139.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2674-664-CM26</t>
+          <t>3713-95-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,37 +712,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>29139.03</v>
+        <v>36317.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3713-95-CM26</t>
+          <t>3713-96-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>36317.99</v>
+        <v>762.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3713-96-CM26</t>
+          <t>1483330-6-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.981.490-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHACABUCO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>762.03</v>
+        <v>26647.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1483330-6-CM26</t>
+          <t>1483330-7-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26647.14</v>
+        <v>1073.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1483330-7-CM26</t>
+          <t>3506-597-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -966,27 +966,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.981.490-8</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA CHACABUCO</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1073.16</v>
+        <v>29985.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3506-597-CM26</t>
+          <t>2387-364-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>29985.76</v>
+        <v>72037.42999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2387-364-CM26</t>
+          <t>2324-1056-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,32 +1083,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>72037.42999999999</v>
+        <v>44713.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2324-1056-CM26</t>
+          <t>1078113-17-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,27 +1149,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>44713.44</v>
+        <v>30092.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1078113-17-CM26</t>
+          <t>1456835-12-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,27 +1210,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>61.981.430-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL LITORAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>30092.14</v>
+        <v>27051.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1456835-12-CM26</t>
+          <t>4062-576-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,27 +1271,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.981.430-4</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL LITORAL</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>27051.14</v>
+        <v>29080.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4062-576-CM26</t>
+          <t>804962-127-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,32 +1327,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>29080.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>804962-127-CM26</t>
+          <t>804962-126-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>23825.17</v>
       </c>
     </row>
     <row r="17">
@@ -1551,7 +1551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>804962-126-CM26</t>
+          <t>527481-81-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>23825.17</v>
+        <v>30303.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>527481-81-CM26</t>
+          <t>4494-589-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,27 +1637,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>77.050.575-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30303.8</v>
+        <v>16391.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4494-589-CM26</t>
+          <t>4494-590-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16391.94</v>
+        <v>1092.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4494-590-CM26</t>
+          <t>2416-201-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1092.05</v>
+        <v>42840</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2416-201-CM26</t>
+          <t>4118-31-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,32 +1815,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>42840</v>
+        <v>27195.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4118-31-CM26</t>
+          <t>5611-72-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>27195.83</v>
+        <v>26735.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5611-72-CM26</t>
+          <t>4118-32-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>26735.86</v>
+        <v>59679.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4118-32-CM26</t>
+          <t>2381-984-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,32 +1998,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>59679.82</v>
+        <v>39602.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2381-984-CM26</t>
+          <t>2731-681-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,37 +2054,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>39602.47</v>
+        <v>17246.81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2731-681-CM26</t>
+          <t>3963-29-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>69.080.900-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>I MUNICIPALIDAD DE PEUMO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>17246.81</v>
+        <v>48853.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3963-29-CM26</t>
+          <t>3666-34-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,37 +2176,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.080.900-1</t>
+          <t>69.071.600-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEUMO</t>
+          <t>I MUNICIPALIDAD DE TIL TIL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>48853.59</v>
+        <v>360.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3666-34-CM26</t>
+          <t>3666-33-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>360.76</v>
+        <v>19962.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3666-33-CM26</t>
+          <t>3666-31-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>19962.46</v>
+        <v>40991.8</v>
       </c>
     </row>
     <row r="32">
@@ -2405,7 +2405,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3666-31-CM26</t>
+          <t>3666-32-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>40991.8</v>
+        <v>736.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3666-32-CM26</t>
+          <t>3880-394-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,37 +2481,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.071.600-3</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIL TIL</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>736.76</v>
+        <v>56890.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3880-394-CM26</t>
+          <t>1078113-21-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,37 +2542,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>56890.75</v>
+        <v>280.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1078113-21-CM26</t>
+          <t>4374-44-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,32 +2608,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>280.05</v>
+        <v>25010.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4374-44-CM26</t>
+          <t>2404-1028-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,27 +2674,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>25010.09</v>
+        <v>39230.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2404-1028-CM26</t>
+          <t>4177-100-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,32 +2730,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>39230.06</v>
+        <v>25368.27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4177-100-CM26</t>
+          <t>4062-605-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2791,32 +2791,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>77.262.067-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>25368.27</v>
+        <v>27525.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4062-605-CM26</t>
+          <t>4125-110-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,27 +2857,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>70.766.500-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.262.067-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>27525.07</v>
+        <v>38588.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4125-110-CM26</t>
+          <t>640840-148-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,27 +2918,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.766.500-9</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>38588.16</v>
+        <v>37712.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>640840-148-CM26</t>
+          <t>759-298-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,32 +2974,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>37712.43</v>
+        <v>25475.68</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>759-298-CM26</t>
+          <t>759-299-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>25475.68</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>759-299-CM26</t>
+          <t>2776-548-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,37 +3091,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>33.7</v>
+        <v>38916.73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2776-548-CM26</t>
+          <t>2675-373-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>38916.73</v>
+        <v>12972.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2675-373-CM26</t>
+          <t>1596-199-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,43 +3223,47 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>12972.86</v>
+        <v>113982.42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1596-199-CM26</t>
+          <t>3326-455-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,22 +3283,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3307,24 +3311,20 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>113982.42</v>
+        <v>29282.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3326-455-CM26</t>
+          <t>3326-457-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>29282.78</v>
+        <v>43132.89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3326-457-CM26</t>
+          <t>4062-621-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,27 +3410,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>43132.89</v>
+        <v>62193.77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4062-621-CM26</t>
+          <t>1501728-57-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3471,27 +3471,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>62193.77</v>
+        <v>47565.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1501728-57-CM26</t>
+          <t>4844-60-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,27 +3532,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>47565.79</v>
+        <v>71799.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4844-60-CM26</t>
+          <t>4844-61-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>71799.47</v>
+        <v>2964.74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4844-61-CM26</t>
+          <t>3754-198-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3654,27 +3654,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2964.74</v>
+        <v>36103.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3754-198-CM26</t>
+          <t>1431841-1057-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3715,17 +3715,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>36103.2</v>
+        <v>22706.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1431841-1057-CM26</t>
+          <t>3659-742-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3776,27 +3776,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22706.01</v>
+        <v>33492.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3659-742-CM26</t>
+          <t>3887-303-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3837,27 +3837,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>33492.34</v>
+        <v>25838.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3887-303-CM26</t>
+          <t>1036569-128-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,27 +3898,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>83.019.900-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>25838.53</v>
+        <v>46798.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1036569-128-CM26</t>
+          <t>2483-560-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3959,27 +3959,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>83.019.900-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,67 +3989,6 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>46798.67</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2483-560-CM26</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>69.071.300-4</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>SUMMIT MOTORS S.A.</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="n">
         <v>216182.5</v>
       </c>
     </row>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
@@ -562,7 +562,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>77.050.575-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>77.050.575-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2102,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2167,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2232,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2297,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2362,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2427,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2553,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2679,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2744,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2809,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2935,11 @@
           <t>77.262.067-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3000,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3065,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3130,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3195,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3260,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3455,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3520,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3585,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3650,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3837,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3902,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3967,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4032,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2041,7 +2041,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2618,7 +2622,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2952,7 +2960,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4125-110-CM26</t>
+          <t>2675-370-SE26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2977,32 +2985,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.766.500-9</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3011,13 +3019,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>38588.16</v>
+        <v>66453.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>640840-148-CM26</t>
+          <t>4125-110-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3032,7 +3040,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3042,32 +3050,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>70.766.500-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3076,13 +3084,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>37712.43</v>
+        <v>38588.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>759-298-CM26</t>
+          <t>759-299-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3102,7 +3110,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3141,13 +3149,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>25475.68</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>759-299-CM26</t>
+          <t>640840-148-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3172,32 +3180,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.001.000-8</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3206,13 +3214,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>33.7</v>
+        <v>37712.43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2776-548-CM26</t>
+          <t>759-298-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3227,7 +3235,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3237,27 +3245,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.001.000-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3271,13 +3279,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>38916.73</v>
+        <v>25475.68</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2675-373-CM26</t>
+          <t>2776-548-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3297,17 +3305,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3317,12 +3325,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3336,13 +3344,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12972.86</v>
+        <v>38916.73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1596-199-CM26</t>
+          <t>2675-373-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3357,7 +3365,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3367,27 +3375,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3401,13 +3409,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>113982.42</v>
+        <v>12972.86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3326-455-CM26</t>
+          <t>1596-199-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3427,22 +3435,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3466,13 +3474,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>29282.78</v>
+        <v>113982.42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3326-457-CM26</t>
+          <t>3326-455-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3512,12 +3520,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3531,13 +3539,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>43132.89</v>
+        <v>29282.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4062-621-CM26</t>
+          <t>3326-457-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3552,37 +3560,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3596,13 +3604,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>62193.77</v>
+        <v>43132.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1501728-57-CM26</t>
+          <t>4062-621-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3627,32 +3635,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3661,13 +3669,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>47565.79</v>
+        <v>62193.77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4844-60-CM26</t>
+          <t>1501728-57-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3682,7 +3690,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3692,43 +3700,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>71799.47</v>
+        <v>47565.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4844-61-CM26</t>
+          <t>4844-60-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3783,13 +3795,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2964.74</v>
+        <v>71799.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3754-198-CM26</t>
+          <t>4844-61-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3814,47 +3826,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>36103.2</v>
+        <v>2964.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1431841-1057-CM26</t>
+          <t>3754-198-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3879,17 +3887,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3913,13 +3921,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22706.01</v>
+        <v>36103.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3659-742-CM26</t>
+          <t>1431841-1057-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3944,32 +3952,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3978,13 +3986,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>33492.34</v>
+        <v>22706.01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3887-303-CM26</t>
+          <t>3659-742-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4009,32 +4017,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4043,13 +4051,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>25838.53</v>
+        <v>33492.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1036569-128-CM26</t>
+          <t>3887-303-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4064,7 +4072,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4074,43 +4082,47 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.390-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>83.019.900-4</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>46798.67</v>
+        <v>25838.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2483-560-CM26</t>
+          <t>1036569-128-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4135,27 +4147,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>62.000.390-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>TATTERSALL AUTOMOTRIZ S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>83.019.900-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4165,6 +4177,67 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
+        <v>46798.67</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2483-560-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.071.300-4</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>216182.5</v>
       </c>
     </row>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/ago-2026.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
